--- a/api/2/clv3/xlsx/pt/SectorGroup.xlsx
+++ b/api/2/clv3/xlsx/pt/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Educação, nível não especificado</t>
+  </si>
+  <si>
+    <t>Educação</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Educação, nível não especificado</t>
-  </si>
-  <si>
-    <t>Educação</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Ensino primário</t>
   </si>
   <si>
+    <t>Ensino básico</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Ensino básico</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Segundo ciclo do ensino secundário (modificado e inclui dados do 11322)</t>
   </si>
   <si>
+    <t>Ensino secundário</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Ensino secundário</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Ensino superior</t>
   </si>
   <si>
+    <t>Ensino pós-secundário</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Ensino pós-secundário</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>Política e gestão administrativa da saúde</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Saúde, geral</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Saúde, geral</t>
-  </si>
-  <si>
-    <t>Saúde</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Cuidados de saúde básica</t>
   </si>
   <si>
+    <t>Saúde básica</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Saúde básica</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -259,12 +259,12 @@
     <t>Controle de DNT, geral</t>
   </si>
   <si>
+    <t>Doenças não transmissíveis (DNT)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Doenças não transmissíveis (DNT)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -409,18 +409,18 @@
     <t>Política e gestão administrativa do setor público</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Governo e sociedade civil, geral</t>
+  </si>
+  <si>
+    <t>Governo e sociedade civil</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Governo e sociedade civil, geral</t>
-  </si>
-  <si>
-    <t>Governo e sociedade civil</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -517,12 +517,12 @@
     <t>Gestão e reforma do sistema de segurança</t>
   </si>
   <si>
+    <t>Conflitos, paz e segurança</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflitos, paz e segurança</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -709,18 +709,18 @@
     <t>Política e gestão administrativa da energia</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Política energética</t>
+  </si>
+  <si>
+    <t>Energia</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Política energética</t>
-  </si>
-  <si>
-    <t>Energia</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Geração de energia, fontes renováveis ​​– várias tecnologias</t>
   </si>
   <si>
+    <t>Geração de energia, fontes renováveis</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Geração de energia, fontes renováveis</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -805,12 +805,12 @@
     <t>Geração de energia, fontes não renováveis, não especificadas</t>
   </si>
   <si>
+    <t>Geração de energia, fontes não renováveis</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Geração de energia, fontes não renováveis</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -847,36 +847,36 @@
     <t>Centrais de energia elétricas de energia híbrida</t>
   </si>
   <si>
+    <t>Centrais de energia híbridas</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Centrais de energia híbridas</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Centrais de energia nucleares e segurança nuclear</t>
   </si>
   <si>
+    <t>Centrais de energia nuclear</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Centrais de energia nuclear</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Centrais de aquecimento</t>
   </si>
   <si>
+    <t>Distribuição de energia</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Distribuição de energia</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>Política e gestão administrativa da agricultura</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agricultura</t>
+  </si>
+  <si>
+    <t>Agricultura, Silvicultura, Pesca</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agricultura</t>
-  </si>
-  <si>
-    <t>Agricultura, Silvicultura, Pesca</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1111,12 +1111,12 @@
     <t>Política e gestão administrativa da silvicultura</t>
   </si>
   <si>
+    <t>Silvicultura</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Silvicultura</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1153,12 +1153,12 @@
     <t>Política e gestão administrativa da pesca</t>
   </si>
   <si>
+    <t>Pesca</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Pesca</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1189,18 +1189,18 @@
     <t>Política e gestão administrativa da indústria</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Indústria</t>
+  </si>
+  <si>
+    <t>Indústria, extractivas, construção</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Indústria</t>
-  </si>
-  <si>
-    <t>Indústria, extractivas, construção</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Política e gestão administrativa dos minerais/minas</t>
   </si>
   <si>
+    <t>Recursos minerais e mineração</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Recursos minerais e mineração</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1381,10 +1381,10 @@
     <t>Política e gestão administrativa da construção</t>
   </si>
   <si>
+    <t>Construção</t>
+  </si>
+  <si>
     <t>323</t>
-  </si>
-  <si>
-    <t>Construção</t>
   </si>
   <si>
     <t>33110</t>
@@ -2184,16 +2184,16 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2207,16 +2207,16 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
         <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2230,16 +2230,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2253,16 +2253,16 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2276,16 +2276,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2299,16 +2299,16 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>23</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2322,16 +2322,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>22</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>23</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2345,16 +2345,16 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2368,16 +2368,16 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>38</v>
       </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>39</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2391,16 +2391,16 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
         <v>44</v>
       </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>45</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2414,16 +2414,16 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
         <v>45</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2529,16 +2529,16 @@
         <v>9</v>
       </c>
       <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
         <v>62</v>
       </c>
-      <c r="E21" t="s">
-        <v>51</v>
-      </c>
       <c r="F21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" t="s">
         <v>63</v>
-      </c>
-      <c r="G21" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2552,16 +2552,16 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
         <v>62</v>
       </c>
-      <c r="E22" t="s">
-        <v>51</v>
-      </c>
       <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" t="s">
         <v>63</v>
-      </c>
-      <c r="G22" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2575,16 +2575,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
         <v>62</v>
       </c>
-      <c r="E23" t="s">
-        <v>51</v>
-      </c>
       <c r="F23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" t="s">
         <v>63</v>
-      </c>
-      <c r="G23" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2598,16 +2598,16 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
         <v>62</v>
       </c>
-      <c r="E24" t="s">
-        <v>51</v>
-      </c>
       <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" t="s">
         <v>63</v>
-      </c>
-      <c r="G24" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2621,16 +2621,16 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" t="s">
         <v>62</v>
       </c>
-      <c r="E25" t="s">
-        <v>51</v>
-      </c>
       <c r="F25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" t="s">
         <v>63</v>
-      </c>
-      <c r="G25" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2644,16 +2644,16 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s">
         <v>62</v>
       </c>
-      <c r="E26" t="s">
-        <v>51</v>
-      </c>
       <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
         <v>63</v>
-      </c>
-      <c r="G26" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2667,16 +2667,16 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" t="s">
         <v>62</v>
       </c>
-      <c r="E27" t="s">
-        <v>51</v>
-      </c>
       <c r="F27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" t="s">
         <v>63</v>
-      </c>
-      <c r="G27" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2687,16 +2687,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
         <v>62</v>
       </c>
-      <c r="E28" t="s">
-        <v>51</v>
-      </c>
       <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" t="s">
         <v>63</v>
-      </c>
-      <c r="G28" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2710,16 +2710,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
         <v>62</v>
       </c>
-      <c r="E29" t="s">
-        <v>51</v>
-      </c>
       <c r="F29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" t="s">
         <v>63</v>
-      </c>
-      <c r="G29" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2733,16 +2733,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" t="s">
         <v>81</v>
       </c>
-      <c r="E30" t="s">
-        <v>51</v>
-      </c>
       <c r="F30" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" t="s">
         <v>82</v>
-      </c>
-      <c r="G30" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2756,16 +2756,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" t="s">
         <v>81</v>
       </c>
-      <c r="E31" t="s">
-        <v>51</v>
-      </c>
       <c r="F31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" t="s">
         <v>82</v>
-      </c>
-      <c r="G31" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2779,16 +2779,16 @@
         <v>9</v>
       </c>
       <c r="D32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" t="s">
         <v>81</v>
       </c>
-      <c r="E32" t="s">
-        <v>51</v>
-      </c>
       <c r="F32" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" t="s">
         <v>82</v>
-      </c>
-      <c r="G32" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2802,16 +2802,16 @@
         <v>9</v>
       </c>
       <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
         <v>81</v>
       </c>
-      <c r="E33" t="s">
-        <v>51</v>
-      </c>
       <c r="F33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" t="s">
         <v>82</v>
-      </c>
-      <c r="G33" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2825,16 +2825,16 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
         <v>81</v>
       </c>
-      <c r="E34" t="s">
-        <v>51</v>
-      </c>
       <c r="F34" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" t="s">
         <v>82</v>
-      </c>
-      <c r="G34" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2848,16 +2848,16 @@
         <v>9</v>
       </c>
       <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
         <v>81</v>
       </c>
-      <c r="E35" t="s">
-        <v>51</v>
-      </c>
       <c r="F35" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" t="s">
         <v>82</v>
-      </c>
-      <c r="G35" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2874,13 +2874,13 @@
         <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F36" t="s">
         <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2897,13 +2897,13 @@
         <v>95</v>
       </c>
       <c r="E37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F37" t="s">
         <v>96</v>
       </c>
       <c r="G37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2920,13 +2920,13 @@
         <v>95</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F38" t="s">
         <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2943,13 +2943,13 @@
         <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F39" t="s">
         <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2966,13 +2966,13 @@
         <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F40" t="s">
         <v>96</v>
       </c>
       <c r="G40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2989,13 +2989,13 @@
         <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F41" t="s">
         <v>108</v>
       </c>
       <c r="G41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3012,13 +3012,13 @@
         <v>107</v>
       </c>
       <c r="E42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F42" t="s">
         <v>108</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3035,13 +3035,13 @@
         <v>107</v>
       </c>
       <c r="E43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F43" t="s">
         <v>108</v>
       </c>
       <c r="G43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3058,13 +3058,13 @@
         <v>107</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F44" t="s">
         <v>108</v>
       </c>
       <c r="G44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3081,13 +3081,13 @@
         <v>107</v>
       </c>
       <c r="E45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F45" t="s">
         <v>108</v>
       </c>
       <c r="G45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3104,13 +3104,13 @@
         <v>107</v>
       </c>
       <c r="E46" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F46" t="s">
         <v>108</v>
       </c>
       <c r="G46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3127,13 +3127,13 @@
         <v>107</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
         <v>108</v>
       </c>
       <c r="G47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3150,13 +3150,13 @@
         <v>107</v>
       </c>
       <c r="E48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F48" t="s">
         <v>108</v>
       </c>
       <c r="G48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3173,13 +3173,13 @@
         <v>107</v>
       </c>
       <c r="E49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F49" t="s">
         <v>108</v>
       </c>
       <c r="G49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3196,13 +3196,13 @@
         <v>107</v>
       </c>
       <c r="E50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F50" t="s">
         <v>108</v>
       </c>
       <c r="G50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3219,13 +3219,13 @@
         <v>107</v>
       </c>
       <c r="E51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F51" t="s">
         <v>108</v>
       </c>
       <c r="G51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3607,16 +3607,16 @@
         <v>9</v>
       </c>
       <c r="D68" t="s">
+        <v>131</v>
+      </c>
+      <c r="E68" t="s">
         <v>167</v>
       </c>
-      <c r="E68" t="s">
-        <v>132</v>
-      </c>
       <c r="F68" t="s">
+        <v>133</v>
+      </c>
+      <c r="G68" t="s">
         <v>168</v>
-      </c>
-      <c r="G68" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3630,16 +3630,16 @@
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" t="s">
         <v>167</v>
       </c>
-      <c r="E69" t="s">
-        <v>132</v>
-      </c>
       <c r="F69" t="s">
+        <v>133</v>
+      </c>
+      <c r="G69" t="s">
         <v>168</v>
-      </c>
-      <c r="G69" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3653,16 +3653,16 @@
         <v>9</v>
       </c>
       <c r="D70" t="s">
+        <v>131</v>
+      </c>
+      <c r="E70" t="s">
         <v>167</v>
       </c>
-      <c r="E70" t="s">
-        <v>132</v>
-      </c>
       <c r="F70" t="s">
+        <v>133</v>
+      </c>
+      <c r="G70" t="s">
         <v>168</v>
-      </c>
-      <c r="G70" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3676,16 +3676,16 @@
         <v>9</v>
       </c>
       <c r="D71" t="s">
+        <v>131</v>
+      </c>
+      <c r="E71" t="s">
         <v>167</v>
       </c>
-      <c r="E71" t="s">
-        <v>132</v>
-      </c>
       <c r="F71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G71" t="s">
         <v>168</v>
-      </c>
-      <c r="G71" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3699,16 +3699,16 @@
         <v>9</v>
       </c>
       <c r="D72" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" t="s">
         <v>167</v>
       </c>
-      <c r="E72" t="s">
-        <v>132</v>
-      </c>
       <c r="F72" t="s">
+        <v>133</v>
+      </c>
+      <c r="G72" t="s">
         <v>168</v>
-      </c>
-      <c r="G72" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3722,16 +3722,16 @@
         <v>9</v>
       </c>
       <c r="D73" t="s">
+        <v>131</v>
+      </c>
+      <c r="E73" t="s">
         <v>167</v>
       </c>
-      <c r="E73" t="s">
-        <v>132</v>
-      </c>
       <c r="F73" t="s">
+        <v>133</v>
+      </c>
+      <c r="G73" t="s">
         <v>168</v>
-      </c>
-      <c r="G73" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3748,13 +3748,13 @@
         <v>181</v>
       </c>
       <c r="E74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F74" t="s">
         <v>182</v>
       </c>
       <c r="G74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3771,13 +3771,13 @@
         <v>181</v>
       </c>
       <c r="E75" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F75" t="s">
         <v>182</v>
       </c>
       <c r="G75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3794,13 +3794,13 @@
         <v>181</v>
       </c>
       <c r="E76" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F76" t="s">
         <v>182</v>
       </c>
       <c r="G76" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3817,13 +3817,13 @@
         <v>181</v>
       </c>
       <c r="E77" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F77" t="s">
         <v>182</v>
       </c>
       <c r="G77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3840,13 +3840,13 @@
         <v>181</v>
       </c>
       <c r="E78" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F78" t="s">
         <v>182</v>
       </c>
       <c r="G78" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3863,13 +3863,13 @@
         <v>181</v>
       </c>
       <c r="E79" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F79" t="s">
         <v>182</v>
       </c>
       <c r="G79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3886,13 +3886,13 @@
         <v>181</v>
       </c>
       <c r="E80" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F80" t="s">
         <v>182</v>
       </c>
       <c r="G80" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3909,13 +3909,13 @@
         <v>181</v>
       </c>
       <c r="E81" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F81" t="s">
         <v>182</v>
       </c>
       <c r="G81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3932,13 +3932,13 @@
         <v>181</v>
       </c>
       <c r="E82" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F82" t="s">
         <v>182</v>
       </c>
       <c r="G82" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3955,13 +3955,13 @@
         <v>181</v>
       </c>
       <c r="E83" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
         <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3978,13 +3978,13 @@
         <v>181</v>
       </c>
       <c r="E84" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
         <v>182</v>
       </c>
       <c r="G84" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -4001,13 +4001,13 @@
         <v>205</v>
       </c>
       <c r="E85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F85" t="s">
         <v>206</v>
       </c>
       <c r="G85" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -4024,13 +4024,13 @@
         <v>205</v>
       </c>
       <c r="E86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
         <v>206</v>
       </c>
       <c r="G86" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -4047,13 +4047,13 @@
         <v>205</v>
       </c>
       <c r="E87" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F87" t="s">
         <v>206</v>
       </c>
       <c r="G87" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -4070,13 +4070,13 @@
         <v>205</v>
       </c>
       <c r="E88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F88" t="s">
         <v>206</v>
       </c>
       <c r="G88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -4093,13 +4093,13 @@
         <v>205</v>
       </c>
       <c r="E89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F89" t="s">
         <v>206</v>
       </c>
       <c r="G89" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -4116,13 +4116,13 @@
         <v>205</v>
       </c>
       <c r="E90" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F90" t="s">
         <v>206</v>
       </c>
       <c r="G90" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -4139,13 +4139,13 @@
         <v>205</v>
       </c>
       <c r="E91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F91" t="s">
         <v>206</v>
       </c>
       <c r="G91" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4162,13 +4162,13 @@
         <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F92" t="s">
         <v>222</v>
       </c>
       <c r="G92" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -4185,13 +4185,13 @@
         <v>221</v>
       </c>
       <c r="E93" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F93" t="s">
         <v>222</v>
       </c>
       <c r="G93" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -4208,13 +4208,13 @@
         <v>221</v>
       </c>
       <c r="E94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F94" t="s">
         <v>222</v>
       </c>
       <c r="G94" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4231,13 +4231,13 @@
         <v>221</v>
       </c>
       <c r="E95" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F95" t="s">
         <v>222</v>
       </c>
       <c r="G95" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4343,16 +4343,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" t="s">
         <v>243</v>
       </c>
-      <c r="E100" t="s">
-        <v>232</v>
-      </c>
       <c r="F100" t="s">
+        <v>233</v>
+      </c>
+      <c r="G100" t="s">
         <v>244</v>
-      </c>
-      <c r="G100" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4366,16 +4366,16 @@
         <v>9</v>
       </c>
       <c r="D101" t="s">
+        <v>231</v>
+      </c>
+      <c r="E101" t="s">
         <v>243</v>
       </c>
-      <c r="E101" t="s">
-        <v>232</v>
-      </c>
       <c r="F101" t="s">
+        <v>233</v>
+      </c>
+      <c r="G101" t="s">
         <v>244</v>
-      </c>
-      <c r="G101" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4389,16 +4389,16 @@
         <v>9</v>
       </c>
       <c r="D102" t="s">
+        <v>231</v>
+      </c>
+      <c r="E102" t="s">
         <v>243</v>
       </c>
-      <c r="E102" t="s">
-        <v>232</v>
-      </c>
       <c r="F102" t="s">
+        <v>233</v>
+      </c>
+      <c r="G102" t="s">
         <v>244</v>
-      </c>
-      <c r="G102" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4412,16 +4412,16 @@
         <v>9</v>
       </c>
       <c r="D103" t="s">
+        <v>231</v>
+      </c>
+      <c r="E103" t="s">
         <v>243</v>
       </c>
-      <c r="E103" t="s">
-        <v>232</v>
-      </c>
       <c r="F103" t="s">
+        <v>233</v>
+      </c>
+      <c r="G103" t="s">
         <v>244</v>
-      </c>
-      <c r="G103" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4435,16 +4435,16 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
+        <v>231</v>
+      </c>
+      <c r="E104" t="s">
         <v>243</v>
       </c>
-      <c r="E104" t="s">
-        <v>232</v>
-      </c>
       <c r="F104" t="s">
+        <v>233</v>
+      </c>
+      <c r="G104" t="s">
         <v>244</v>
-      </c>
-      <c r="G104" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4458,16 +4458,16 @@
         <v>9</v>
       </c>
       <c r="D105" t="s">
+        <v>231</v>
+      </c>
+      <c r="E105" t="s">
         <v>243</v>
       </c>
-      <c r="E105" t="s">
-        <v>232</v>
-      </c>
       <c r="F105" t="s">
+        <v>233</v>
+      </c>
+      <c r="G105" t="s">
         <v>244</v>
-      </c>
-      <c r="G105" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4481,16 +4481,16 @@
         <v>9</v>
       </c>
       <c r="D106" t="s">
+        <v>231</v>
+      </c>
+      <c r="E106" t="s">
         <v>243</v>
       </c>
-      <c r="E106" t="s">
-        <v>232</v>
-      </c>
       <c r="F106" t="s">
+        <v>233</v>
+      </c>
+      <c r="G106" t="s">
         <v>244</v>
-      </c>
-      <c r="G106" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4504,16 +4504,16 @@
         <v>9</v>
       </c>
       <c r="D107" t="s">
+        <v>231</v>
+      </c>
+      <c r="E107" t="s">
         <v>243</v>
       </c>
-      <c r="E107" t="s">
-        <v>232</v>
-      </c>
       <c r="F107" t="s">
+        <v>233</v>
+      </c>
+      <c r="G107" t="s">
         <v>244</v>
-      </c>
-      <c r="G107" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4527,16 +4527,16 @@
         <v>9</v>
       </c>
       <c r="D108" t="s">
+        <v>231</v>
+      </c>
+      <c r="E108" t="s">
         <v>243</v>
       </c>
-      <c r="E108" t="s">
-        <v>232</v>
-      </c>
       <c r="F108" t="s">
+        <v>233</v>
+      </c>
+      <c r="G108" t="s">
         <v>244</v>
-      </c>
-      <c r="G108" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4550,16 +4550,16 @@
         <v>9</v>
       </c>
       <c r="D109" t="s">
+        <v>231</v>
+      </c>
+      <c r="E109" t="s">
         <v>263</v>
       </c>
-      <c r="E109" t="s">
-        <v>232</v>
-      </c>
       <c r="F109" t="s">
+        <v>233</v>
+      </c>
+      <c r="G109" t="s">
         <v>264</v>
-      </c>
-      <c r="G109" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4573,16 +4573,16 @@
         <v>9</v>
       </c>
       <c r="D110" t="s">
+        <v>231</v>
+      </c>
+      <c r="E110" t="s">
         <v>263</v>
       </c>
-      <c r="E110" t="s">
-        <v>232</v>
-      </c>
       <c r="F110" t="s">
+        <v>233</v>
+      </c>
+      <c r="G110" t="s">
         <v>264</v>
-      </c>
-      <c r="G110" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4596,16 +4596,16 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
+        <v>231</v>
+      </c>
+      <c r="E111" t="s">
         <v>263</v>
       </c>
-      <c r="E111" t="s">
-        <v>232</v>
-      </c>
       <c r="F111" t="s">
+        <v>233</v>
+      </c>
+      <c r="G111" t="s">
         <v>264</v>
-      </c>
-      <c r="G111" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4619,16 +4619,16 @@
         <v>9</v>
       </c>
       <c r="D112" t="s">
+        <v>231</v>
+      </c>
+      <c r="E112" t="s">
         <v>263</v>
       </c>
-      <c r="E112" t="s">
-        <v>232</v>
-      </c>
       <c r="F112" t="s">
+        <v>233</v>
+      </c>
+      <c r="G112" t="s">
         <v>264</v>
-      </c>
-      <c r="G112" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4642,16 +4642,16 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
+        <v>231</v>
+      </c>
+      <c r="E113" t="s">
         <v>263</v>
       </c>
-      <c r="E113" t="s">
-        <v>232</v>
-      </c>
       <c r="F113" t="s">
+        <v>233</v>
+      </c>
+      <c r="G113" t="s">
         <v>264</v>
-      </c>
-      <c r="G113" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4665,16 +4665,16 @@
         <v>9</v>
       </c>
       <c r="D114" t="s">
+        <v>231</v>
+      </c>
+      <c r="E114" t="s">
         <v>263</v>
       </c>
-      <c r="E114" t="s">
-        <v>232</v>
-      </c>
       <c r="F114" t="s">
+        <v>233</v>
+      </c>
+      <c r="G114" t="s">
         <v>264</v>
-      </c>
-      <c r="G114" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4688,16 +4688,16 @@
         <v>9</v>
       </c>
       <c r="D115" t="s">
+        <v>231</v>
+      </c>
+      <c r="E115" t="s">
         <v>277</v>
       </c>
-      <c r="E115" t="s">
-        <v>232</v>
-      </c>
       <c r="F115" t="s">
+        <v>233</v>
+      </c>
+      <c r="G115" t="s">
         <v>278</v>
-      </c>
-      <c r="G115" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4711,16 +4711,16 @@
         <v>9</v>
       </c>
       <c r="D116" t="s">
+        <v>231</v>
+      </c>
+      <c r="E116" t="s">
         <v>281</v>
       </c>
-      <c r="E116" t="s">
-        <v>232</v>
-      </c>
       <c r="F116" t="s">
+        <v>233</v>
+      </c>
+      <c r="G116" t="s">
         <v>282</v>
-      </c>
-      <c r="G116" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4734,16 +4734,16 @@
         <v>9</v>
       </c>
       <c r="D117" t="s">
+        <v>231</v>
+      </c>
+      <c r="E117" t="s">
         <v>285</v>
       </c>
-      <c r="E117" t="s">
-        <v>232</v>
-      </c>
       <c r="F117" t="s">
+        <v>233</v>
+      </c>
+      <c r="G117" t="s">
         <v>286</v>
-      </c>
-      <c r="G117" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4757,16 +4757,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
+        <v>231</v>
+      </c>
+      <c r="E118" t="s">
         <v>285</v>
       </c>
-      <c r="E118" t="s">
-        <v>232</v>
-      </c>
       <c r="F118" t="s">
+        <v>233</v>
+      </c>
+      <c r="G118" t="s">
         <v>286</v>
-      </c>
-      <c r="G118" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4780,16 +4780,16 @@
         <v>9</v>
       </c>
       <c r="D119" t="s">
+        <v>231</v>
+      </c>
+      <c r="E119" t="s">
         <v>285</v>
       </c>
-      <c r="E119" t="s">
-        <v>232</v>
-      </c>
       <c r="F119" t="s">
+        <v>233</v>
+      </c>
+      <c r="G119" t="s">
         <v>286</v>
-      </c>
-      <c r="G119" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4803,16 +4803,16 @@
         <v>9</v>
       </c>
       <c r="D120" t="s">
+        <v>231</v>
+      </c>
+      <c r="E120" t="s">
         <v>285</v>
       </c>
-      <c r="E120" t="s">
-        <v>232</v>
-      </c>
       <c r="F120" t="s">
+        <v>233</v>
+      </c>
+      <c r="G120" t="s">
         <v>286</v>
-      </c>
-      <c r="G120" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4826,16 +4826,16 @@
         <v>9</v>
       </c>
       <c r="D121" t="s">
+        <v>231</v>
+      </c>
+      <c r="E121" t="s">
         <v>285</v>
       </c>
-      <c r="E121" t="s">
-        <v>232</v>
-      </c>
       <c r="F121" t="s">
+        <v>233</v>
+      </c>
+      <c r="G121" t="s">
         <v>286</v>
-      </c>
-      <c r="G121" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>9</v>
       </c>
       <c r="D122" t="s">
+        <v>231</v>
+      </c>
+      <c r="E122" t="s">
         <v>285</v>
       </c>
-      <c r="E122" t="s">
-        <v>232</v>
-      </c>
       <c r="F122" t="s">
+        <v>233</v>
+      </c>
+      <c r="G122" t="s">
         <v>286</v>
-      </c>
-      <c r="G122" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4872,16 +4872,16 @@
         <v>9</v>
       </c>
       <c r="D123" t="s">
+        <v>231</v>
+      </c>
+      <c r="E123" t="s">
         <v>285</v>
       </c>
-      <c r="E123" t="s">
-        <v>232</v>
-      </c>
       <c r="F123" t="s">
+        <v>233</v>
+      </c>
+      <c r="G123" t="s">
         <v>286</v>
-      </c>
-      <c r="G123" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>301</v>
       </c>
       <c r="E124" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F124" t="s">
         <v>302</v>
       </c>
       <c r="G124" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4921,13 +4921,13 @@
         <v>301</v>
       </c>
       <c r="E125" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F125" t="s">
         <v>302</v>
       </c>
       <c r="G125" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4944,13 +4944,13 @@
         <v>301</v>
       </c>
       <c r="E126" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F126" t="s">
         <v>302</v>
       </c>
       <c r="G126" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4967,13 +4967,13 @@
         <v>301</v>
       </c>
       <c r="E127" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F127" t="s">
         <v>302</v>
       </c>
       <c r="G127" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>301</v>
       </c>
       <c r="E128" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F128" t="s">
         <v>302</v>
       </c>
       <c r="G128" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -5013,13 +5013,13 @@
         <v>301</v>
       </c>
       <c r="E129" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F129" t="s">
         <v>302</v>
       </c>
       <c r="G129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -5036,13 +5036,13 @@
         <v>315</v>
       </c>
       <c r="E130" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F130" t="s">
         <v>316</v>
       </c>
       <c r="G130" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -5059,13 +5059,13 @@
         <v>315</v>
       </c>
       <c r="E131" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F131" t="s">
         <v>316</v>
       </c>
       <c r="G131" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -5082,13 +5082,13 @@
         <v>315</v>
       </c>
       <c r="E132" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F132" t="s">
         <v>316</v>
       </c>
       <c r="G132" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -5105,13 +5105,13 @@
         <v>315</v>
       </c>
       <c r="E133" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F133" t="s">
         <v>316</v>
       </c>
       <c r="G133" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5539,16 +5539,16 @@
         <v>9</v>
       </c>
       <c r="D152" t="s">
+        <v>325</v>
+      </c>
+      <c r="E152" t="s">
         <v>365</v>
       </c>
-      <c r="E152" t="s">
-        <v>326</v>
-      </c>
       <c r="F152" t="s">
+        <v>327</v>
+      </c>
+      <c r="G152" t="s">
         <v>366</v>
-      </c>
-      <c r="G152" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5562,16 +5562,16 @@
         <v>9</v>
       </c>
       <c r="D153" t="s">
+        <v>325</v>
+      </c>
+      <c r="E153" t="s">
         <v>365</v>
       </c>
-      <c r="E153" t="s">
-        <v>326</v>
-      </c>
       <c r="F153" t="s">
+        <v>327</v>
+      </c>
+      <c r="G153" t="s">
         <v>366</v>
-      </c>
-      <c r="G153" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5585,16 +5585,16 @@
         <v>9</v>
       </c>
       <c r="D154" t="s">
+        <v>325</v>
+      </c>
+      <c r="E154" t="s">
         <v>365</v>
       </c>
-      <c r="E154" t="s">
-        <v>326</v>
-      </c>
       <c r="F154" t="s">
+        <v>327</v>
+      </c>
+      <c r="G154" t="s">
         <v>366</v>
-      </c>
-      <c r="G154" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5608,16 +5608,16 @@
         <v>9</v>
       </c>
       <c r="D155" t="s">
+        <v>325</v>
+      </c>
+      <c r="E155" t="s">
         <v>365</v>
       </c>
-      <c r="E155" t="s">
-        <v>326</v>
-      </c>
       <c r="F155" t="s">
+        <v>327</v>
+      </c>
+      <c r="G155" t="s">
         <v>366</v>
-      </c>
-      <c r="G155" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5631,16 +5631,16 @@
         <v>9</v>
       </c>
       <c r="D156" t="s">
+        <v>325</v>
+      </c>
+      <c r="E156" t="s">
         <v>365</v>
       </c>
-      <c r="E156" t="s">
-        <v>326</v>
-      </c>
       <c r="F156" t="s">
+        <v>327</v>
+      </c>
+      <c r="G156" t="s">
         <v>366</v>
-      </c>
-      <c r="G156" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5654,16 +5654,16 @@
         <v>9</v>
       </c>
       <c r="D157" t="s">
+        <v>325</v>
+      </c>
+      <c r="E157" t="s">
         <v>365</v>
       </c>
-      <c r="E157" t="s">
-        <v>326</v>
-      </c>
       <c r="F157" t="s">
+        <v>327</v>
+      </c>
+      <c r="G157" t="s">
         <v>366</v>
-      </c>
-      <c r="G157" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5677,16 +5677,16 @@
         <v>9</v>
       </c>
       <c r="D158" t="s">
+        <v>325</v>
+      </c>
+      <c r="E158" t="s">
         <v>379</v>
       </c>
-      <c r="E158" t="s">
-        <v>326</v>
-      </c>
       <c r="F158" t="s">
+        <v>327</v>
+      </c>
+      <c r="G158" t="s">
         <v>380</v>
-      </c>
-      <c r="G158" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5700,16 +5700,16 @@
         <v>9</v>
       </c>
       <c r="D159" t="s">
+        <v>325</v>
+      </c>
+      <c r="E159" t="s">
         <v>379</v>
       </c>
-      <c r="E159" t="s">
-        <v>326</v>
-      </c>
       <c r="F159" t="s">
+        <v>327</v>
+      </c>
+      <c r="G159" t="s">
         <v>380</v>
-      </c>
-      <c r="G159" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5723,16 +5723,16 @@
         <v>9</v>
       </c>
       <c r="D160" t="s">
+        <v>325</v>
+      </c>
+      <c r="E160" t="s">
         <v>379</v>
       </c>
-      <c r="E160" t="s">
-        <v>326</v>
-      </c>
       <c r="F160" t="s">
+        <v>327</v>
+      </c>
+      <c r="G160" t="s">
         <v>380</v>
-      </c>
-      <c r="G160" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5746,16 +5746,16 @@
         <v>9</v>
       </c>
       <c r="D161" t="s">
+        <v>325</v>
+      </c>
+      <c r="E161" t="s">
         <v>379</v>
       </c>
-      <c r="E161" t="s">
-        <v>326</v>
-      </c>
       <c r="F161" t="s">
+        <v>327</v>
+      </c>
+      <c r="G161" t="s">
         <v>380</v>
-      </c>
-      <c r="G161" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5769,16 +5769,16 @@
         <v>9</v>
       </c>
       <c r="D162" t="s">
+        <v>325</v>
+      </c>
+      <c r="E162" t="s">
         <v>379</v>
       </c>
-      <c r="E162" t="s">
-        <v>326</v>
-      </c>
       <c r="F162" t="s">
+        <v>327</v>
+      </c>
+      <c r="G162" t="s">
         <v>380</v>
-      </c>
-      <c r="G162" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6229,16 +6229,16 @@
         <v>9</v>
       </c>
       <c r="D182" t="s">
+        <v>391</v>
+      </c>
+      <c r="E182" t="s">
         <v>433</v>
       </c>
-      <c r="E182" t="s">
-        <v>392</v>
-      </c>
       <c r="F182" t="s">
+        <v>393</v>
+      </c>
+      <c r="G182" t="s">
         <v>434</v>
-      </c>
-      <c r="G182" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6252,16 +6252,16 @@
         <v>9</v>
       </c>
       <c r="D183" t="s">
+        <v>391</v>
+      </c>
+      <c r="E183" t="s">
         <v>433</v>
       </c>
-      <c r="E183" t="s">
-        <v>392</v>
-      </c>
       <c r="F183" t="s">
+        <v>393</v>
+      </c>
+      <c r="G183" t="s">
         <v>434</v>
-      </c>
-      <c r="G183" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6275,16 +6275,16 @@
         <v>9</v>
       </c>
       <c r="D184" t="s">
+        <v>391</v>
+      </c>
+      <c r="E184" t="s">
         <v>433</v>
       </c>
-      <c r="E184" t="s">
-        <v>392</v>
-      </c>
       <c r="F184" t="s">
+        <v>393</v>
+      </c>
+      <c r="G184" t="s">
         <v>434</v>
-      </c>
-      <c r="G184" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6298,16 +6298,16 @@
         <v>9</v>
       </c>
       <c r="D185" t="s">
+        <v>391</v>
+      </c>
+      <c r="E185" t="s">
         <v>433</v>
       </c>
-      <c r="E185" t="s">
-        <v>392</v>
-      </c>
       <c r="F185" t="s">
+        <v>393</v>
+      </c>
+      <c r="G185" t="s">
         <v>434</v>
-      </c>
-      <c r="G185" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6321,16 +6321,16 @@
         <v>9</v>
       </c>
       <c r="D186" t="s">
+        <v>391</v>
+      </c>
+      <c r="E186" t="s">
         <v>433</v>
       </c>
-      <c r="E186" t="s">
-        <v>392</v>
-      </c>
       <c r="F186" t="s">
+        <v>393</v>
+      </c>
+      <c r="G186" t="s">
         <v>434</v>
-      </c>
-      <c r="G186" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6344,16 +6344,16 @@
         <v>9</v>
       </c>
       <c r="D187" t="s">
+        <v>391</v>
+      </c>
+      <c r="E187" t="s">
         <v>433</v>
       </c>
-      <c r="E187" t="s">
-        <v>392</v>
-      </c>
       <c r="F187" t="s">
+        <v>393</v>
+      </c>
+      <c r="G187" t="s">
         <v>434</v>
-      </c>
-      <c r="G187" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6367,16 +6367,16 @@
         <v>9</v>
       </c>
       <c r="D188" t="s">
+        <v>391</v>
+      </c>
+      <c r="E188" t="s">
         <v>433</v>
       </c>
-      <c r="E188" t="s">
-        <v>392</v>
-      </c>
       <c r="F188" t="s">
+        <v>393</v>
+      </c>
+      <c r="G188" t="s">
         <v>434</v>
-      </c>
-      <c r="G188" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6390,16 +6390,16 @@
         <v>9</v>
       </c>
       <c r="D189" t="s">
+        <v>391</v>
+      </c>
+      <c r="E189" t="s">
         <v>433</v>
       </c>
-      <c r="E189" t="s">
-        <v>392</v>
-      </c>
       <c r="F189" t="s">
+        <v>393</v>
+      </c>
+      <c r="G189" t="s">
         <v>434</v>
-      </c>
-      <c r="G189" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6413,16 +6413,16 @@
         <v>9</v>
       </c>
       <c r="D190" t="s">
+        <v>391</v>
+      </c>
+      <c r="E190" t="s">
         <v>433</v>
       </c>
-      <c r="E190" t="s">
-        <v>392</v>
-      </c>
       <c r="F190" t="s">
+        <v>393</v>
+      </c>
+      <c r="G190" t="s">
         <v>434</v>
-      </c>
-      <c r="G190" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6436,16 +6436,16 @@
         <v>9</v>
       </c>
       <c r="D191" t="s">
+        <v>391</v>
+      </c>
+      <c r="E191" t="s">
         <v>433</v>
       </c>
-      <c r="E191" t="s">
-        <v>392</v>
-      </c>
       <c r="F191" t="s">
+        <v>393</v>
+      </c>
+      <c r="G191" t="s">
         <v>434</v>
-      </c>
-      <c r="G191" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6459,16 +6459,16 @@
         <v>9</v>
       </c>
       <c r="D192" t="s">
+        <v>391</v>
+      </c>
+      <c r="E192" t="s">
         <v>455</v>
       </c>
-      <c r="E192" t="s">
-        <v>392</v>
-      </c>
       <c r="F192" t="s">
+        <v>393</v>
+      </c>
+      <c r="G192" t="s">
         <v>456</v>
-      </c>
-      <c r="G192" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6485,13 +6485,13 @@
         <v>459</v>
       </c>
       <c r="E193" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F193" t="s">
         <v>460</v>
       </c>
       <c r="G193" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6508,13 +6508,13 @@
         <v>459</v>
       </c>
       <c r="E194" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F194" t="s">
         <v>460</v>
       </c>
       <c r="G194" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6531,13 +6531,13 @@
         <v>459</v>
       </c>
       <c r="E195" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F195" t="s">
         <v>460</v>
       </c>
       <c r="G195" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6554,13 +6554,13 @@
         <v>459</v>
       </c>
       <c r="E196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F196" t="s">
         <v>460</v>
       </c>
       <c r="G196" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6577,13 +6577,13 @@
         <v>459</v>
       </c>
       <c r="E197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F197" t="s">
         <v>460</v>
       </c>
       <c r="G197" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6600,13 +6600,13 @@
         <v>459</v>
       </c>
       <c r="E198" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F198" t="s">
         <v>460</v>
       </c>
       <c r="G198" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6623,13 +6623,13 @@
         <v>473</v>
       </c>
       <c r="E199" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F199" t="s">
         <v>474</v>
       </c>
       <c r="G199" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6646,13 +6646,13 @@
         <v>477</v>
       </c>
       <c r="E200" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F200" t="s">
         <v>478</v>
       </c>
       <c r="G200" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6669,13 +6669,13 @@
         <v>477</v>
       </c>
       <c r="E201" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F201" t="s">
         <v>478</v>
       </c>
       <c r="G201" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6692,13 +6692,13 @@
         <v>477</v>
       </c>
       <c r="E202" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F202" t="s">
         <v>478</v>
       </c>
       <c r="G202" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6715,13 +6715,13 @@
         <v>477</v>
       </c>
       <c r="E203" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F203" t="s">
         <v>478</v>
       </c>
       <c r="G203" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6738,13 +6738,13 @@
         <v>477</v>
       </c>
       <c r="E204" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F204" t="s">
         <v>478</v>
       </c>
       <c r="G204" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6761,13 +6761,13 @@
         <v>477</v>
       </c>
       <c r="E205" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F205" t="s">
         <v>478</v>
       </c>
       <c r="G205" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6784,13 +6784,13 @@
         <v>491</v>
       </c>
       <c r="E206" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F206" t="s">
         <v>492</v>
       </c>
       <c r="G206" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6807,13 +6807,13 @@
         <v>491</v>
       </c>
       <c r="E207" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F207" t="s">
         <v>492</v>
       </c>
       <c r="G207" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6830,13 +6830,13 @@
         <v>491</v>
       </c>
       <c r="E208" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F208" t="s">
         <v>492</v>
       </c>
       <c r="G208" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6853,13 +6853,13 @@
         <v>491</v>
       </c>
       <c r="E209" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F209" t="s">
         <v>492</v>
       </c>
       <c r="G209" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6876,13 +6876,13 @@
         <v>491</v>
       </c>
       <c r="E210" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F210" t="s">
         <v>492</v>
       </c>
       <c r="G210" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6899,13 +6899,13 @@
         <v>491</v>
       </c>
       <c r="E211" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F211" t="s">
         <v>492</v>
       </c>
       <c r="G211" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6922,13 +6922,13 @@
         <v>491</v>
       </c>
       <c r="E212" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F212" t="s">
         <v>492</v>
       </c>
       <c r="G212" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6945,13 +6945,13 @@
         <v>491</v>
       </c>
       <c r="E213" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F213" t="s">
         <v>492</v>
       </c>
       <c r="G213" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6968,13 +6968,13 @@
         <v>491</v>
       </c>
       <c r="E214" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F214" t="s">
         <v>492</v>
       </c>
       <c r="G214" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6991,13 +6991,13 @@
         <v>491</v>
       </c>
       <c r="E215" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F215" t="s">
         <v>492</v>
       </c>
       <c r="G215" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -7014,13 +7014,13 @@
         <v>513</v>
       </c>
       <c r="E216" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F216" t="s">
         <v>514</v>
       </c>
       <c r="G216" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -7037,13 +7037,13 @@
         <v>517</v>
       </c>
       <c r="E217" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F217" t="s">
         <v>518</v>
       </c>
       <c r="G217" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -7060,13 +7060,13 @@
         <v>521</v>
       </c>
       <c r="E218" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F218" t="s">
         <v>522</v>
       </c>
       <c r="G218" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -7083,13 +7083,13 @@
         <v>521</v>
       </c>
       <c r="E219" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F219" t="s">
         <v>522</v>
       </c>
       <c r="G219" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -7106,13 +7106,13 @@
         <v>527</v>
       </c>
       <c r="E220" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F220" t="s">
         <v>526</v>
       </c>
       <c r="G220" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -7129,13 +7129,13 @@
         <v>527</v>
       </c>
       <c r="E221" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F221" t="s">
         <v>526</v>
       </c>
       <c r="G221" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -7152,13 +7152,13 @@
         <v>527</v>
       </c>
       <c r="E222" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F222" t="s">
         <v>526</v>
       </c>
       <c r="G222" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -7175,13 +7175,13 @@
         <v>527</v>
       </c>
       <c r="E223" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F223" t="s">
         <v>526</v>
       </c>
       <c r="G223" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -7198,13 +7198,13 @@
         <v>527</v>
       </c>
       <c r="E224" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F224" t="s">
         <v>526</v>
       </c>
       <c r="G224" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -7221,13 +7221,13 @@
         <v>527</v>
       </c>
       <c r="E225" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F225" t="s">
         <v>526</v>
       </c>
       <c r="G225" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -7244,13 +7244,13 @@
         <v>527</v>
       </c>
       <c r="E226" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F226" t="s">
         <v>526</v>
       </c>
       <c r="G226" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -7267,13 +7267,13 @@
         <v>542</v>
       </c>
       <c r="E227" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F227" t="s">
         <v>543</v>
       </c>
       <c r="G227" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -7290,13 +7290,13 @@
         <v>542</v>
       </c>
       <c r="E228" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F228" t="s">
         <v>543</v>
       </c>
       <c r="G228" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -7313,13 +7313,13 @@
         <v>542</v>
       </c>
       <c r="E229" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F229" t="s">
         <v>543</v>
       </c>
       <c r="G229" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -7336,13 +7336,13 @@
         <v>550</v>
       </c>
       <c r="E230" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F230" t="s">
         <v>551</v>
       </c>
       <c r="G230" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -7359,13 +7359,13 @@
         <v>554</v>
       </c>
       <c r="E231" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F231" t="s">
         <v>555</v>
       </c>
       <c r="G231" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -7382,13 +7382,13 @@
         <v>558</v>
       </c>
       <c r="E232" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F232" t="s">
         <v>559</v>
       </c>
       <c r="G232" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -7405,13 +7405,13 @@
         <v>562</v>
       </c>
       <c r="E233" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F233" t="s">
         <v>563</v>
       </c>
       <c r="G233" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -7428,13 +7428,13 @@
         <v>566</v>
       </c>
       <c r="E234" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F234" t="s">
         <v>567</v>
       </c>
       <c r="G234" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7451,13 +7451,13 @@
         <v>566</v>
       </c>
       <c r="E235" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F235" t="s">
         <v>567</v>
       </c>
       <c r="G235" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
